--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_116_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_116_R12.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5103</v>
+        <v>5.9889</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8674</v>
+        <v>5.1779</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6429</v>
+        <v>0.8109</v>
       </c>
       <c r="G2" t="n">
         <v>5.4678</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3519</v>
+        <v>0.1267</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9709</v>
+        <v>-0.6603</v>
       </c>
       <c r="U2" t="n">
-        <v>0.619</v>
+        <v>0.787</v>
       </c>
       <c r="V2" t="n">
         <v>0.3943</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2456</v>
+        <v>5.3118</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4087</v>
+        <v>3.8482</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8368</v>
+        <v>1.4636</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5826</v>
+        <v>4.6079</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4814</v>
+        <v>2.3996</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1013</v>
+        <v>2.2083</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0858</v>
+        <v>4.6472</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7141</v>
+        <v>2.1713</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3717</v>
+        <v>2.4759</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4968</v>
+        <v>-0.0393</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2327</v>
+        <v>0.2283</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7296</v>
+        <v>-0.2676</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1268</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8215</v>
+        <v>-0.4795</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9483</v>
+        <v>0.3978</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>0.3217</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.7504999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8764</v>
+        <v>4.8429</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5809</v>
+        <v>1.6446</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2956</v>
+        <v>3.1983</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6079</v>
+        <v>3.5826</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3996</v>
+        <v>1.4814</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2083</v>
+        <v>2.1013</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6472</v>
+        <v>3.0858</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1713</v>
+        <v>1.7141</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4759</v>
+        <v>1.3717</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0393</v>
+        <v>0.4968</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2283</v>
+        <v>-0.2327</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2676</v>
+        <v>0.7296</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5171</v>
+        <v>0.7242</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7468</v>
+        <v>-0.5856</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2298</v>
+        <v>1.3098</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3217</v>
+        <v>0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7504999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5111</v>
+        <v>4.2146</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3099</v>
+        <v>2.6519</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2012</v>
+        <v>1.5627</v>
       </c>
       <c r="G5" t="n">
         <v>2.6631</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4389</v>
+        <v>0.1423</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7468</v>
+        <v>-0.4048</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1857</v>
+        <v>0.5472</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2144</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4952</v>
+        <v>2.0306</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5416</v>
+        <v>1.604</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9536</v>
+        <v>0.4266</v>
       </c>
       <c r="G6" t="n">
-        <v>1.401</v>
+        <v>1.9933</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7623</v>
+        <v>0.695</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3613</v>
+        <v>1.2982</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9013</v>
+        <v>1.6787</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6805</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2208</v>
+        <v>1.141</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5003</v>
+        <v>0.3145</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0818</v>
+        <v>0.1573</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5821</v>
+        <v>0.1573</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1668</v>
+        <v>0.0373</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1098</v>
+        <v>-0.0747</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2766</v>
+        <v>0.112</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0727</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9634</v>
+        <v>1.9711</v>
       </c>
       <c r="E7" t="n">
-        <v>1.604</v>
+        <v>0.2191</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3593</v>
+        <v>1.7519</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9933</v>
+        <v>1.401</v>
       </c>
       <c r="H7" t="n">
-        <v>0.695</v>
+        <v>1.7623</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2982</v>
+        <v>-0.3613</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6787</v>
+        <v>1.9013</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.6805</v>
       </c>
       <c r="L7" t="n">
-        <v>1.141</v>
+        <v>0.2208</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3145</v>
+        <v>-0.5003</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1573</v>
+        <v>0.0818</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>-0.5821</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0299</v>
+        <v>0.6427</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0747</v>
+        <v>-0.4323</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0448</v>
+        <v>1.075</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.0727</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2144</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1624</v>
+        <v>1.3788</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1718</v>
+        <v>-1.5939</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3342</v>
+        <v>2.9727</v>
       </c>
       <c r="G8" t="n">
         <v>1.9403</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0996</v>
+        <v>0.1169</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9709</v>
+        <v>-0.393</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1287</v>
+        <v>0.5098</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2144</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0255</v>
+        <v>0.3167</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5843</v>
+        <v>-2.5589</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5589</v>
+        <v>2.8755</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6175</v>
+        <v>0.5788</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4307</v>
+        <v>-0.3481</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8132</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2995</v>
+        <v>-0.1073</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9996</v>
+        <v>-0.0939</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7001</v>
+        <v>-0.0134</v>
       </c>
       <c r="M9" t="n">
-        <v>0.318</v>
+        <v>0.6861</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5688</v>
+        <v>-0.2543</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8868</v>
+        <v>0.9403</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1606</v>
+        <v>-0.1024</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6765</v>
+        <v>-0.4362</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4841</v>
+        <v>0.3339</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.7527</v>
+        <v>0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.7527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0061</v>
+        <v>-0.2216</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8695</v>
+        <v>0.0083</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8755</v>
+        <v>-0.2299</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5788</v>
+        <v>0.6079</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3481</v>
+        <v>0.0625</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.5454</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1073</v>
+        <v>0.1576</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0939</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0134</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6861</v>
+        <v>0.4502</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2543</v>
+        <v>-0.0216</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9403</v>
+        <v>0.4718</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4129</v>
+        <v>0.0108</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7468</v>
+        <v>-0.1494</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3339</v>
+        <v>0.1601</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.188</v>
+        <v>-0.6418</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0083</v>
+        <v>0.7154</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1963</v>
+        <v>-1.3572</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6079</v>
+        <v>2.6175</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0625</v>
+        <v>3.4307</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5454</v>
+        <v>-0.8132</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1576</v>
+        <v>2.2995</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08400000000000001</v>
+        <v>3.9996</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0736</v>
+        <v>-1.7001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4502</v>
+        <v>0.318</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0216</v>
+        <v>-0.5688</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4718</v>
+        <v>0.8868</v>
       </c>
       <c r="P11" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0444</v>
+        <v>0.4933</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1494</v>
+        <v>-0.1924</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1937</v>
+        <v>0.6858</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-3.7527</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1814</v>
+        <v>-0.7125</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4118</v>
+        <v>-2.1445</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2304</v>
+        <v>1.432</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2254</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6361</v>
+        <v>-0.1672</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6721</v>
+        <v>-0.4048</v>
       </c>
       <c r="U12" t="n">
-        <v>0.036</v>
+        <v>0.2377</v>
       </c>
       <c r="V12" t="n">
         <v>1.5356</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8717</v>
+        <v>-1.8044</v>
       </c>
       <c r="E13" t="n">
         <v>-1.8273</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0444</v>
+        <v>0.0228</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7696</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2618</v>
+        <v>-0.1946</v>
       </c>
       <c r="T13" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2609</v>
+        <v>0.3282</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5361</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.5549</v>
+        <v>22.6751</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6247</v>
+        <v>7.744799999999999</v>
       </c>
       <c r="F14" t="n">
         <v>14.9299</v>
@@ -1519,7 +1519,7 @@
         <v>10.5064</v>
       </c>
       <c r="J14" t="n">
-        <v>22.5363</v>
+        <v>22.53629999999999</v>
       </c>
       <c r="K14" t="n">
         <v>13.8213</v>
@@ -1528,7 +1528,7 @@
         <v>8.715199999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9287000000000002</v>
+        <v>0.9286999999999997</v>
       </c>
       <c r="N14" t="n">
         <v>-0.8624000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>16.2366</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6282000000000003</v>
+        <v>1.7483</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.856000000000001</v>
+        <v>-4.7358</v>
       </c>
       <c r="U14" t="n">
-        <v>6.4841</v>
+        <v>6.4843</v>
       </c>
       <c r="V14" t="n">
         <v>-2.5387</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6498</v>
+        <v>3.1044</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5228</v>
+        <v>1.8766</v>
       </c>
       <c r="F15" t="n">
-        <v>1.127</v>
+        <v>1.2278</v>
       </c>
       <c r="G15" t="n">
         <v>0.492</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5381</v>
+        <v>-0.0835</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9709</v>
+        <v>-0.617</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4327</v>
+        <v>0.5335</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5541</v>
+        <v>0.513</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1204</v>
+        <v>2.2354</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4336</v>
+        <v>-1.7224</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.568</v>
+        <v>-1.7721</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.012</v>
+        <v>0.898</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.556</v>
+        <v>-2.6701</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4814</v>
+        <v>1.4195</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8605</v>
+        <v>2.4535</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3419</v>
+        <v>-1.0341</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0866</v>
+        <v>-3.1916</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8726</v>
+        <v>-1.5556</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.214</v>
+        <v>-1.636</v>
       </c>
       <c r="P16" t="n">
         <v>1.6237</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0345</v>
+        <v>-0.4107</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6018</v>
+        <v>-1.0965</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4327</v>
+        <v>0.6858</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1084</v>
+        <v>-0.1708</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7636</v>
+        <v>-0.7052</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6552</v>
+        <v>0.5344</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7721</v>
+        <v>-1.568</v>
       </c>
       <c r="H17" t="n">
-        <v>0.898</v>
+        <v>-0.012</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.6701</v>
+        <v>-1.556</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4195</v>
+        <v>-0.4814</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4535</v>
+        <v>0.8605</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0341</v>
+        <v>-1.3419</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1916</v>
+        <v>-1.0866</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5556</v>
+        <v>-0.8726</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.636</v>
+        <v>-0.214</v>
       </c>
       <c r="P17" t="n">
         <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8153</v>
+        <v>0.3097</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5683</v>
+        <v>-0.2238</v>
       </c>
       <c r="U17" t="n">
-        <v>0.753</v>
+        <v>0.5335</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3033</v>
+        <v>-0.8759</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1904</v>
+        <v>-0.6622</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1129</v>
+        <v>-0.2137</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6357</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8685</v>
+        <v>0.2959</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. DINWIDDIE</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9495</v>
+        <v>-1.3601</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.223</v>
+        <v>-1.3668</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2735</v>
+        <v>0.0066</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.0895</v>
+        <v>-1.6897</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.2329</v>
+        <v>-1.683</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8566</v>
+        <v>-0.0067</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0444</v>
+        <v>0.1621</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6665</v>
+        <v>-0.4636</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6222</v>
+        <v>0.6257</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0451</v>
+        <v>-1.8518</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5664</v>
+        <v>-1.2195</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4787</v>
+        <v>-0.6323</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4415</v>
+        <v>-0.0442</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9313</v>
+        <v>-0.5109</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3728</v>
+        <v>0.4668</v>
       </c>
       <c r="V19" t="n">
-        <v>2.0026</v>
+        <v>0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>S. DINWIDDIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8313</v>
+        <v>-1.4371</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6027</v>
+        <v>-1.341</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2286</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6897</v>
+        <v>-4.0895</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.683</v>
+        <v>-3.2329</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0067</v>
+        <v>-0.8566</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1621</v>
+        <v>-1.0444</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4636</v>
+        <v>-1.6665</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6257</v>
+        <v>0.6222</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8518</v>
+        <v>-3.0451</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2195</v>
+        <v>-1.5664</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6323</v>
+        <v>-1.4787</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5153</v>
+        <v>-0.0461</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7468</v>
+        <v>-1.0493</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2315</v>
+        <v>1.0031</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1418</v>
+        <v>2.0026</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2712</v>
+        <v>-2.1704</v>
       </c>
       <c r="E21" t="n">
         <v>-1.4338</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8373</v>
+        <v>-0.7365</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0293</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.0187</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.433</v>
+        <v>-2.6689</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4318</v>
+        <v>-1.6677</v>
       </c>
       <c r="F22" t="n">
         <v>-1.0012</v>
@@ -2170,10 +2170,10 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.637</v>
+        <v>0.4011</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U22" t="n">
         <v>0.3734</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3936</v>
+        <v>-2.8694</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4368</v>
+        <v>-1.9764</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0432</v>
+        <v>-0.8929</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1289</v>
+        <v>-1.152</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9411</v>
+        <v>0.3637</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1878</v>
+        <v>-1.5157</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4452</v>
+        <v>1.6715</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7324000000000001</v>
+        <v>1.9193</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7127</v>
+        <v>-0.2477</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6838</v>
+        <v>-2.8235</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2087</v>
+        <v>-1.5556</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4751</v>
+        <v>-1.2679</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2689</v>
+        <v>-0.4854</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6721</v>
+        <v>-1.0965</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.6111</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4084</v>
+        <v>-3.4265</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4482</v>
+        <v>-4.2009</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9602000000000001</v>
+        <v>0.7744</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.152</v>
+        <v>-3.1289</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3637</v>
+        <v>-1.9411</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5157</v>
+        <v>-1.1878</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6715</v>
+        <v>-1.4452</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9193</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2477</v>
+        <v>-0.7127</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8235</v>
+        <v>-1.6838</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5556</v>
+        <v>-1.2087</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2679</v>
+        <v>-0.4751</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0244</v>
+        <v>0.2359</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5683</v>
+        <v>-0.4362</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.6721</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="25">
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1042</v>
+        <v>-4.8683</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1208</v>
+        <v>-2.8849</v>
       </c>
       <c r="F25" t="n">
         <v>-1.9834</v>
@@ -2404,10 +2404,10 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6879</v>
+        <v>-0.452</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1949</v>
+        <v>-0.959</v>
       </c>
       <c r="U25" t="n">
         <v>0.507</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.1726</v>
+        <v>-5.3248</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4494</v>
+        <v>-2.8032</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.7232</v>
+        <v>-2.5216</v>
       </c>
       <c r="G26" t="n">
         <v>-2.581</v>
@@ -2482,13 +2482,13 @@
         <v>0.9278</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2153</v>
+        <v>-0.3675</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1098</v>
+        <v>-0.4637</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1054</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-2.1444</v>
@@ -2521,7 +2521,7 @@
         <v>-14.9301</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.624700000000001</v>
+        <v>-6.624699999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-23.4653</v>
@@ -2533,10 +2533,10 @@
         <v>-10.5066</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9289000000000003</v>
+        <v>-0.9288999999999998</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8625000000000003</v>
+        <v>0.8624999999999998</v>
       </c>
       <c r="L27" t="n">
         <v>-1.7913</v>
@@ -2560,13 +2560,13 @@
         <v>16.2368</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6280000000000001</v>
+        <v>-0.6281000000000001</v>
       </c>
       <c r="T27" t="n">
         <v>-6.4841</v>
       </c>
       <c r="U27" t="n">
-        <v>5.855999999999999</v>
+        <v>5.8559</v>
       </c>
       <c r="V27" t="n">
         <v>2.5387</v>
